--- a/notebooks/rda-experiments/runs/v12-sample3/evaluation_results.xlsx
+++ b/notebooks/rda-experiments/runs/v12-sample3/evaluation_results.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2703" uniqueCount="185">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2685" uniqueCount="185">
   <si>
     <t>fields in reference</t>
   </si>
@@ -512,10 +512,10 @@
     <t>Software generated under the project will be released under the GNU Public License, and available for free download on the labs’ websites. This includes code for each of our 3 experimental systems.</t>
   </si>
   <si>
+    <t>only 57% of the model's words are in the reference</t>
+  </si>
+  <si>
     <t>only 0% of the model's words are in the reference</t>
-  </si>
-  <si>
-    <t>only 57% of the model's words are in the reference</t>
   </si>
   <si>
     <t>only 21% of the model's words are in the reference</t>
@@ -1020,31 +1020,31 @@
         <v>66</v>
       </c>
       <c r="D3">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E3">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F3">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G3">
-        <v>0.485</v>
+        <v>0.5</v>
       </c>
       <c r="H3">
-        <v>0.52</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="I3">
-        <v>0.502</v>
+        <v>0.528</v>
       </c>
       <c r="J3">
-        <v>0.4102564102564102</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="K3">
-        <v>0.4358974358974359</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="L3">
-        <v>0.1538461538461539</v>
+        <v>0.1428571428571428</v>
       </c>
     </row>
     <row r="4" spans="1:12">
@@ -1058,31 +1058,31 @@
         <v>96</v>
       </c>
       <c r="D4">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E4">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G4">
-        <v>0.542</v>
+        <v>0.552</v>
       </c>
       <c r="H4">
-        <v>0.88</v>
+        <v>0.92</v>
       </c>
       <c r="I4">
-        <v>0.671</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="J4">
-        <v>0.5252525252525253</v>
+        <v>0.5408163265306123</v>
       </c>
       <c r="K4">
-        <v>0.4444444444444444</v>
+        <v>0.4387755102040816</v>
       </c>
       <c r="L4">
-        <v>0.0303030303030303</v>
+        <v>0.02040816326530612</v>
       </c>
     </row>
   </sheetData>
@@ -2681,7 +2681,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G79"/>
+  <dimension ref="A1:G78"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -3020,7 +3020,7 @@
         <v>3</v>
       </c>
       <c r="B18" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="C18" t="s">
         <v>40</v>
@@ -3037,7 +3037,7 @@
         <v>3</v>
       </c>
       <c r="B19" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="C19" t="s">
         <v>41</v>
@@ -3057,7 +3057,7 @@
         <v>3</v>
       </c>
       <c r="B20" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="C20" t="s">
         <v>42</v>
@@ -3077,7 +3077,7 @@
         <v>3</v>
       </c>
       <c r="B21" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="C21" t="s">
         <v>43</v>
@@ -3097,7 +3097,7 @@
         <v>3</v>
       </c>
       <c r="B22" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="C22" t="s">
         <v>44</v>
@@ -3106,13 +3106,13 @@
         <v>156</v>
       </c>
       <c r="E22" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F22" t="s">
         <v>140</v>
       </c>
       <c r="G22" t="s">
-        <v>164</v>
+        <v>142</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -3120,7 +3120,7 @@
         <v>3</v>
       </c>
       <c r="B23" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="C23" t="s">
         <v>45</v>
@@ -3137,7 +3137,7 @@
         <v>3</v>
       </c>
       <c r="B24" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="C24" t="s">
         <v>46</v>
@@ -3154,7 +3154,7 @@
         <v>3</v>
       </c>
       <c r="B25" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="C25" t="s">
         <v>47</v>
@@ -3174,7 +3174,7 @@
         <v>3</v>
       </c>
       <c r="B26" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="C26" t="s">
         <v>50</v>
@@ -3183,13 +3183,10 @@
         <v>157</v>
       </c>
       <c r="E26" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F26" t="s">
-        <v>140</v>
-      </c>
-      <c r="G26" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -3197,7 +3194,7 @@
         <v>3</v>
       </c>
       <c r="B27" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="C27" t="s">
         <v>51</v>
@@ -3363,7 +3360,7 @@
         <v>140</v>
       </c>
       <c r="G35" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -3677,7 +3674,7 @@
         <v>140</v>
       </c>
       <c r="G51" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -3999,10 +3996,10 @@
         <v>3</v>
       </c>
       <c r="B68" t="s">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="E68" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="F68" t="s">
         <v>141</v>
@@ -4013,10 +4010,10 @@
         <v>3</v>
       </c>
       <c r="B69" t="s">
-        <v>57</v>
+        <v>69</v>
       </c>
       <c r="E69" t="s">
-        <v>133</v>
+        <v>117</v>
       </c>
       <c r="F69" t="s">
         <v>141</v>
@@ -4027,10 +4024,10 @@
         <v>3</v>
       </c>
       <c r="B70" t="s">
-        <v>69</v>
+        <v>95</v>
       </c>
       <c r="E70" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="F70" t="s">
         <v>141</v>
@@ -4041,10 +4038,10 @@
         <v>3</v>
       </c>
       <c r="B71" t="s">
-        <v>95</v>
+        <v>74</v>
       </c>
       <c r="E71" t="s">
-        <v>121</v>
+        <v>135</v>
       </c>
       <c r="F71" t="s">
         <v>141</v>
@@ -4055,10 +4052,10 @@
         <v>3</v>
       </c>
       <c r="B72" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E72" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F72" t="s">
         <v>141</v>
@@ -4069,10 +4066,10 @@
         <v>3</v>
       </c>
       <c r="B73" t="s">
-        <v>73</v>
+        <v>96</v>
       </c>
       <c r="E73" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="F73" t="s">
         <v>141</v>
@@ -4083,10 +4080,10 @@
         <v>3</v>
       </c>
       <c r="B74" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E74" t="s">
-        <v>136</v>
+        <v>104</v>
       </c>
       <c r="F74" t="s">
         <v>141</v>
@@ -4097,10 +4094,10 @@
         <v>3</v>
       </c>
       <c r="B75" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E75" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F75" t="s">
         <v>141</v>
@@ -4111,7 +4108,7 @@
         <v>3</v>
       </c>
       <c r="B76" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E76" t="s">
         <v>105</v>
@@ -4125,10 +4122,10 @@
         <v>3</v>
       </c>
       <c r="B77" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E77" t="s">
-        <v>105</v>
+        <v>137</v>
       </c>
       <c r="F77" t="s">
         <v>141</v>
@@ -4139,26 +4136,12 @@
         <v>3</v>
       </c>
       <c r="B78" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E78" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F78" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="79" spans="1:7">
-      <c r="A79">
-        <v>3</v>
-      </c>
-      <c r="B79" t="s">
-        <v>101</v>
-      </c>
-      <c r="E79" t="s">
-        <v>138</v>
-      </c>
-      <c r="F79" t="s">
         <v>141</v>
       </c>
     </row>
@@ -4169,7 +4152,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G100"/>
+  <dimension ref="A1:G99"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -4545,7 +4528,7 @@
         <v>3</v>
       </c>
       <c r="B20" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="C20" t="s">
         <v>40</v>
@@ -4562,7 +4545,7 @@
         <v>3</v>
       </c>
       <c r="B21" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="C21" t="s">
         <v>41</v>
@@ -4582,7 +4565,7 @@
         <v>3</v>
       </c>
       <c r="B22" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="C22" t="s">
         <v>42</v>
@@ -4599,7 +4582,7 @@
         <v>3</v>
       </c>
       <c r="B23" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="C23" t="s">
         <v>43</v>
@@ -4619,7 +4602,7 @@
         <v>3</v>
       </c>
       <c r="B24" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="C24" t="s">
         <v>44</v>
@@ -4628,13 +4611,13 @@
         <v>158</v>
       </c>
       <c r="E24" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F24" t="s">
         <v>140</v>
       </c>
       <c r="G24" t="s">
-        <v>164</v>
+        <v>142</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -4642,7 +4625,7 @@
         <v>3</v>
       </c>
       <c r="B25" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="C25" t="s">
         <v>45</v>
@@ -4659,7 +4642,7 @@
         <v>3</v>
       </c>
       <c r="B26" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="C26" t="s">
         <v>46</v>
@@ -4676,7 +4659,7 @@
         <v>3</v>
       </c>
       <c r="B27" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="C27" t="s">
         <v>47</v>
@@ -4696,7 +4679,7 @@
         <v>3</v>
       </c>
       <c r="B28" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="C28" t="s">
         <v>48</v>
@@ -4713,7 +4696,7 @@
         <v>3</v>
       </c>
       <c r="B29" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="C29" t="s">
         <v>49</v>
@@ -4733,7 +4716,7 @@
         <v>3</v>
       </c>
       <c r="B30" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="C30" t="s">
         <v>50</v>
@@ -4742,13 +4725,10 @@
         <v>157</v>
       </c>
       <c r="E30" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F30" t="s">
-        <v>140</v>
-      </c>
-      <c r="G30" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -4756,7 +4736,7 @@
         <v>3</v>
       </c>
       <c r="B31" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="C31" t="s">
         <v>51</v>
@@ -6042,10 +6022,10 @@
         <v>3</v>
       </c>
       <c r="B98" t="s">
-        <v>44</v>
+        <v>95</v>
       </c>
       <c r="E98" t="s">
-        <v>130</v>
+        <v>121</v>
       </c>
       <c r="F98" t="s">
         <v>141</v>
@@ -6056,26 +6036,12 @@
         <v>3</v>
       </c>
       <c r="B99" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="E99" t="s">
-        <v>121</v>
+        <v>138</v>
       </c>
       <c r="F99" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="100" spans="1:7">
-      <c r="A100">
-        <v>3</v>
-      </c>
-      <c r="B100" t="s">
-        <v>101</v>
-      </c>
-      <c r="E100" t="s">
-        <v>138</v>
-      </c>
-      <c r="F100" t="s">
         <v>141</v>
       </c>
     </row>
@@ -6086,7 +6052,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H260"/>
+  <dimension ref="A1:H258"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -8281,7 +8247,7 @@
         <v>13</v>
       </c>
       <c r="C100" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="D100" t="s">
         <v>40</v>
@@ -8301,7 +8267,7 @@
         <v>13</v>
       </c>
       <c r="C101" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="D101" t="s">
         <v>41</v>
@@ -8324,7 +8290,7 @@
         <v>13</v>
       </c>
       <c r="C102" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="D102" t="s">
         <v>42</v>
@@ -8347,7 +8313,7 @@
         <v>13</v>
       </c>
       <c r="C103" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="D103" t="s">
         <v>43</v>
@@ -8370,7 +8336,7 @@
         <v>13</v>
       </c>
       <c r="C104" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="D104" t="s">
         <v>44</v>
@@ -8379,13 +8345,13 @@
         <v>156</v>
       </c>
       <c r="F104" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="G104" t="s">
         <v>140</v>
       </c>
       <c r="H104" t="s">
-        <v>164</v>
+        <v>142</v>
       </c>
     </row>
     <row r="105" spans="1:8">
@@ -8396,7 +8362,7 @@
         <v>13</v>
       </c>
       <c r="C105" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="D105" t="s">
         <v>45</v>
@@ -8416,7 +8382,7 @@
         <v>13</v>
       </c>
       <c r="C106" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="D106" t="s">
         <v>46</v>
@@ -8436,7 +8402,7 @@
         <v>13</v>
       </c>
       <c r="C107" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="D107" t="s">
         <v>47</v>
@@ -8459,7 +8425,7 @@
         <v>13</v>
       </c>
       <c r="C108" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="D108" t="s">
         <v>50</v>
@@ -8468,13 +8434,10 @@
         <v>157</v>
       </c>
       <c r="F108" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="G108" t="s">
-        <v>140</v>
-      </c>
-      <c r="H108" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
     </row>
     <row r="109" spans="1:8">
@@ -8485,7 +8448,7 @@
         <v>13</v>
       </c>
       <c r="C109" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="D109" t="s">
         <v>51</v>
@@ -8675,7 +8638,7 @@
         <v>140</v>
       </c>
       <c r="H117" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="118" spans="1:8">
@@ -9037,7 +9000,7 @@
         <v>140</v>
       </c>
       <c r="H133" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="134" spans="1:8">
@@ -9410,10 +9373,10 @@
         <v>13</v>
       </c>
       <c r="C150" t="s">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="F150" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="G150" t="s">
         <v>141</v>
@@ -9427,10 +9390,10 @@
         <v>13</v>
       </c>
       <c r="C151" t="s">
-        <v>57</v>
+        <v>69</v>
       </c>
       <c r="F151" t="s">
-        <v>133</v>
+        <v>117</v>
       </c>
       <c r="G151" t="s">
         <v>141</v>
@@ -9444,10 +9407,10 @@
         <v>13</v>
       </c>
       <c r="C152" t="s">
-        <v>69</v>
+        <v>95</v>
       </c>
       <c r="F152" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="G152" t="s">
         <v>141</v>
@@ -9461,10 +9424,10 @@
         <v>13</v>
       </c>
       <c r="C153" t="s">
-        <v>95</v>
+        <v>74</v>
       </c>
       <c r="F153" t="s">
-        <v>121</v>
+        <v>135</v>
       </c>
       <c r="G153" t="s">
         <v>141</v>
@@ -9478,10 +9441,10 @@
         <v>13</v>
       </c>
       <c r="C154" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F154" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="G154" t="s">
         <v>141</v>
@@ -9495,10 +9458,10 @@
         <v>13</v>
       </c>
       <c r="C155" t="s">
-        <v>73</v>
+        <v>96</v>
       </c>
       <c r="F155" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="G155" t="s">
         <v>141</v>
@@ -9512,10 +9475,10 @@
         <v>13</v>
       </c>
       <c r="C156" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F156" t="s">
-        <v>136</v>
+        <v>104</v>
       </c>
       <c r="G156" t="s">
         <v>141</v>
@@ -9529,10 +9492,10 @@
         <v>13</v>
       </c>
       <c r="C157" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F157" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="G157" t="s">
         <v>141</v>
@@ -9546,7 +9509,7 @@
         <v>13</v>
       </c>
       <c r="C158" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F158" t="s">
         <v>105</v>
@@ -9563,10 +9526,10 @@
         <v>13</v>
       </c>
       <c r="C159" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F159" t="s">
-        <v>105</v>
+        <v>137</v>
       </c>
       <c r="G159" t="s">
         <v>141</v>
@@ -9580,10 +9543,10 @@
         <v>13</v>
       </c>
       <c r="C160" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F160" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="G160" t="s">
         <v>141</v>
@@ -9594,16 +9557,22 @@
         <v>3</v>
       </c>
       <c r="B161" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C161" t="s">
-        <v>101</v>
+        <v>22</v>
+      </c>
+      <c r="D161" t="s">
+        <v>22</v>
+      </c>
+      <c r="E161" t="s">
+        <v>102</v>
       </c>
       <c r="F161" t="s">
-        <v>138</v>
+        <v>102</v>
       </c>
       <c r="G161" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
     </row>
     <row r="162" spans="1:8">
@@ -9614,19 +9583,19 @@
         <v>14</v>
       </c>
       <c r="C162" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D162" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E162" t="s">
-        <v>102</v>
-      </c>
-      <c r="F162" t="s">
-        <v>102</v>
+        <v>154</v>
       </c>
       <c r="G162" t="s">
-        <v>139</v>
+        <v>140</v>
+      </c>
+      <c r="H162" t="s">
+        <v>142</v>
       </c>
     </row>
     <row r="163" spans="1:8">
@@ -9637,10 +9606,10 @@
         <v>14</v>
       </c>
       <c r="C163" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D163" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E163" t="s">
         <v>154</v>
@@ -9660,13 +9629,13 @@
         <v>14</v>
       </c>
       <c r="C164" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D164" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E164" t="s">
-        <v>154</v>
+        <v>104</v>
       </c>
       <c r="G164" t="s">
         <v>140</v>
@@ -9683,13 +9652,13 @@
         <v>14</v>
       </c>
       <c r="C165" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D165" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E165" t="s">
-        <v>104</v>
+        <v>181</v>
       </c>
       <c r="G165" t="s">
         <v>140</v>
@@ -9706,19 +9675,16 @@
         <v>14</v>
       </c>
       <c r="C166" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D166" t="s">
-        <v>26</v>
-      </c>
-      <c r="E166" t="s">
-        <v>181</v>
+        <v>27</v>
       </c>
       <c r="G166" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="H166" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="167" spans="1:8">
@@ -9729,16 +9695,19 @@
         <v>14</v>
       </c>
       <c r="C167" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D167" t="s">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="E167" t="s">
+        <v>106</v>
       </c>
       <c r="G167" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="H167" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="168" spans="1:8">
@@ -9749,19 +9718,16 @@
         <v>14</v>
       </c>
       <c r="C168" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D168" t="s">
-        <v>28</v>
-      </c>
-      <c r="E168" t="s">
-        <v>106</v>
+        <v>29</v>
       </c>
       <c r="G168" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="H168" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="169" spans="1:8">
@@ -9772,10 +9738,10 @@
         <v>14</v>
       </c>
       <c r="C169" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D169" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G169" t="s">
         <v>139</v>
@@ -9792,10 +9758,10 @@
         <v>14</v>
       </c>
       <c r="C170" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D170" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G170" t="s">
         <v>139</v>
@@ -9812,16 +9778,19 @@
         <v>14</v>
       </c>
       <c r="C171" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D171" t="s">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="E171" t="s">
+        <v>106</v>
       </c>
       <c r="G171" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="H171" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="172" spans="1:8">
@@ -9832,19 +9801,19 @@
         <v>14</v>
       </c>
       <c r="C172" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D172" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E172" t="s">
-        <v>106</v>
+        <v>128</v>
+      </c>
+      <c r="F172" t="s">
+        <v>128</v>
       </c>
       <c r="G172" t="s">
-        <v>140</v>
-      </c>
-      <c r="H172" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
     </row>
     <row r="173" spans="1:8">
@@ -9855,16 +9824,16 @@
         <v>14</v>
       </c>
       <c r="C173" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D173" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E173" t="s">
-        <v>128</v>
+        <v>108</v>
       </c>
       <c r="F173" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="G173" t="s">
         <v>139</v>
@@ -9878,19 +9847,19 @@
         <v>14</v>
       </c>
       <c r="C174" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D174" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E174" t="s">
-        <v>108</v>
-      </c>
-      <c r="F174" t="s">
-        <v>129</v>
+        <v>109</v>
       </c>
       <c r="G174" t="s">
-        <v>139</v>
+        <v>140</v>
+      </c>
+      <c r="H174" t="s">
+        <v>142</v>
       </c>
     </row>
     <row r="175" spans="1:8">
@@ -9901,19 +9870,19 @@
         <v>14</v>
       </c>
       <c r="C175" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D175" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E175" t="s">
-        <v>109</v>
+        <v>105</v>
+      </c>
+      <c r="F175" t="s">
+        <v>105</v>
       </c>
       <c r="G175" t="s">
-        <v>140</v>
-      </c>
-      <c r="H175" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
     </row>
     <row r="176" spans="1:8">
@@ -9924,10 +9893,10 @@
         <v>14</v>
       </c>
       <c r="C176" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D176" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E176" t="s">
         <v>105</v>
@@ -9947,19 +9916,16 @@
         <v>14</v>
       </c>
       <c r="C177" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D177" t="s">
-        <v>37</v>
-      </c>
-      <c r="E177" t="s">
-        <v>105</v>
-      </c>
-      <c r="F177" t="s">
-        <v>105</v>
+        <v>38</v>
       </c>
       <c r="G177" t="s">
         <v>139</v>
+      </c>
+      <c r="H177" t="s">
+        <v>143</v>
       </c>
     </row>
     <row r="178" spans="1:8">
@@ -9970,16 +9936,19 @@
         <v>14</v>
       </c>
       <c r="C178" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D178" t="s">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="E178" t="s">
+        <v>106</v>
       </c>
       <c r="G178" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="H178" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="179" spans="1:8">
@@ -9990,19 +9959,16 @@
         <v>14</v>
       </c>
       <c r="C179" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="D179" t="s">
-        <v>39</v>
-      </c>
-      <c r="E179" t="s">
-        <v>106</v>
+        <v>40</v>
       </c>
       <c r="G179" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="H179" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="180" spans="1:8">
@@ -10013,16 +9979,19 @@
         <v>14</v>
       </c>
       <c r="C180" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="D180" t="s">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="E180" t="s">
+        <v>111</v>
       </c>
       <c r="G180" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="H180" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="181" spans="1:8">
@@ -10033,19 +10002,16 @@
         <v>14</v>
       </c>
       <c r="C181" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="D181" t="s">
-        <v>41</v>
-      </c>
-      <c r="E181" t="s">
-        <v>111</v>
+        <v>42</v>
       </c>
       <c r="G181" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="H181" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="182" spans="1:8">
@@ -10056,16 +10022,19 @@
         <v>14</v>
       </c>
       <c r="C182" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="D182" t="s">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="E182" t="s">
+        <v>155</v>
       </c>
       <c r="G182" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="H182" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="183" spans="1:8">
@@ -10076,13 +10045,16 @@
         <v>14</v>
       </c>
       <c r="C183" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="D183" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E183" t="s">
-        <v>155</v>
+        <v>158</v>
+      </c>
+      <c r="F183" t="s">
+        <v>131</v>
       </c>
       <c r="G183" t="s">
         <v>140</v>
@@ -10099,22 +10071,16 @@
         <v>14</v>
       </c>
       <c r="C184" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="D184" t="s">
-        <v>44</v>
-      </c>
-      <c r="E184" t="s">
-        <v>158</v>
-      </c>
-      <c r="F184" t="s">
-        <v>130</v>
+        <v>45</v>
       </c>
       <c r="G184" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="H184" t="s">
-        <v>164</v>
+        <v>143</v>
       </c>
     </row>
     <row r="185" spans="1:8">
@@ -10125,10 +10091,10 @@
         <v>14</v>
       </c>
       <c r="C185" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="D185" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G185" t="s">
         <v>139</v>
@@ -10145,16 +10111,19 @@
         <v>14</v>
       </c>
       <c r="C186" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="D186" t="s">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="E186" t="s">
+        <v>111</v>
       </c>
       <c r="G186" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="H186" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="187" spans="1:8">
@@ -10165,19 +10134,16 @@
         <v>14</v>
       </c>
       <c r="C187" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="D187" t="s">
-        <v>47</v>
-      </c>
-      <c r="E187" t="s">
-        <v>111</v>
+        <v>48</v>
       </c>
       <c r="G187" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="H187" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="188" spans="1:8">
@@ -10188,16 +10154,19 @@
         <v>14</v>
       </c>
       <c r="C188" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="D188" t="s">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="E188" t="s">
+        <v>155</v>
       </c>
       <c r="G188" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="H188" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="189" spans="1:8">
@@ -10208,19 +10177,19 @@
         <v>14</v>
       </c>
       <c r="C189" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="D189" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E189" t="s">
-        <v>155</v>
+        <v>157</v>
+      </c>
+      <c r="F189" t="s">
+        <v>130</v>
       </c>
       <c r="G189" t="s">
-        <v>140</v>
-      </c>
-      <c r="H189" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
     </row>
     <row r="190" spans="1:8">
@@ -10231,22 +10200,16 @@
         <v>14</v>
       </c>
       <c r="C190" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="D190" t="s">
-        <v>50</v>
-      </c>
-      <c r="E190" t="s">
-        <v>157</v>
-      </c>
-      <c r="F190" t="s">
-        <v>131</v>
+        <v>51</v>
       </c>
       <c r="G190" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="H190" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="191" spans="1:8">
@@ -10257,16 +10220,19 @@
         <v>14</v>
       </c>
       <c r="C191" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D191" t="s">
-        <v>51</v>
+        <v>52</v>
+      </c>
+      <c r="E191" t="s">
+        <v>117</v>
       </c>
       <c r="G191" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="H191" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="192" spans="1:8">
@@ -10277,13 +10243,13 @@
         <v>14</v>
       </c>
       <c r="C192" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D192" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E192" t="s">
-        <v>117</v>
+        <v>104</v>
       </c>
       <c r="G192" t="s">
         <v>140</v>
@@ -10300,19 +10266,16 @@
         <v>14</v>
       </c>
       <c r="C193" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D193" t="s">
-        <v>53</v>
-      </c>
-      <c r="E193" t="s">
-        <v>104</v>
+        <v>54</v>
       </c>
       <c r="G193" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="H193" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="194" spans="1:8">
@@ -10323,16 +10286,19 @@
         <v>14</v>
       </c>
       <c r="C194" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D194" t="s">
-        <v>54</v>
+        <v>55</v>
+      </c>
+      <c r="E194" t="s">
+        <v>106</v>
       </c>
       <c r="G194" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="H194" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="195" spans="1:8">
@@ -10343,19 +10309,19 @@
         <v>14</v>
       </c>
       <c r="C195" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D195" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E195" t="s">
-        <v>106</v>
+        <v>132</v>
+      </c>
+      <c r="F195" t="s">
+        <v>132</v>
       </c>
       <c r="G195" t="s">
-        <v>140</v>
-      </c>
-      <c r="H195" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
     </row>
     <row r="196" spans="1:8">
@@ -10366,16 +10332,16 @@
         <v>14</v>
       </c>
       <c r="C196" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D196" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E196" t="s">
-        <v>132</v>
+        <v>119</v>
       </c>
       <c r="F196" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="G196" t="s">
         <v>139</v>
@@ -10389,19 +10355,19 @@
         <v>14</v>
       </c>
       <c r="C197" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D197" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E197" t="s">
-        <v>119</v>
-      </c>
-      <c r="F197" t="s">
-        <v>133</v>
+        <v>109</v>
       </c>
       <c r="G197" t="s">
-        <v>139</v>
+        <v>140</v>
+      </c>
+      <c r="H197" t="s">
+        <v>142</v>
       </c>
     </row>
     <row r="198" spans="1:8">
@@ -10412,19 +10378,19 @@
         <v>14</v>
       </c>
       <c r="C198" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D198" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E198" t="s">
-        <v>109</v>
+        <v>105</v>
+      </c>
+      <c r="F198" t="s">
+        <v>105</v>
       </c>
       <c r="G198" t="s">
-        <v>140</v>
-      </c>
-      <c r="H198" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
     </row>
     <row r="199" spans="1:8">
@@ -10435,10 +10401,10 @@
         <v>14</v>
       </c>
       <c r="C199" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D199" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E199" t="s">
         <v>105</v>
@@ -10458,19 +10424,16 @@
         <v>14</v>
       </c>
       <c r="C200" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D200" t="s">
-        <v>60</v>
-      </c>
-      <c r="E200" t="s">
-        <v>105</v>
-      </c>
-      <c r="F200" t="s">
-        <v>105</v>
+        <v>61</v>
       </c>
       <c r="G200" t="s">
         <v>139</v>
+      </c>
+      <c r="H200" t="s">
+        <v>143</v>
       </c>
     </row>
     <row r="201" spans="1:8">
@@ -10481,16 +10444,19 @@
         <v>14</v>
       </c>
       <c r="C201" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D201" t="s">
-        <v>61</v>
+        <v>62</v>
+      </c>
+      <c r="E201" t="s">
+        <v>106</v>
       </c>
       <c r="G201" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="H201" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="202" spans="1:8">
@@ -10501,19 +10467,16 @@
         <v>14</v>
       </c>
       <c r="C202" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D202" t="s">
-        <v>62</v>
-      </c>
-      <c r="E202" t="s">
-        <v>106</v>
+        <v>63</v>
       </c>
       <c r="G202" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="H202" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="203" spans="1:8">
@@ -10524,16 +10487,19 @@
         <v>14</v>
       </c>
       <c r="C203" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D203" t="s">
-        <v>63</v>
+        <v>64</v>
+      </c>
+      <c r="E203" t="s">
+        <v>111</v>
       </c>
       <c r="G203" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="H203" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="204" spans="1:8">
@@ -10544,19 +10510,16 @@
         <v>14</v>
       </c>
       <c r="C204" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D204" t="s">
-        <v>64</v>
-      </c>
-      <c r="E204" t="s">
-        <v>111</v>
+        <v>65</v>
       </c>
       <c r="G204" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="H204" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="205" spans="1:8">
@@ -10567,16 +10530,19 @@
         <v>14</v>
       </c>
       <c r="C205" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D205" t="s">
-        <v>65</v>
+        <v>66</v>
+      </c>
+      <c r="E205" t="s">
+        <v>155</v>
       </c>
       <c r="G205" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="H205" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="206" spans="1:8">
@@ -10587,13 +10553,16 @@
         <v>14</v>
       </c>
       <c r="C206" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D206" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E206" t="s">
-        <v>155</v>
+        <v>158</v>
+      </c>
+      <c r="F206" t="s">
+        <v>131</v>
       </c>
       <c r="G206" t="s">
         <v>140</v>
@@ -10610,22 +10579,16 @@
         <v>14</v>
       </c>
       <c r="C207" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D207" t="s">
-        <v>67</v>
-      </c>
-      <c r="E207" t="s">
-        <v>158</v>
-      </c>
-      <c r="F207" t="s">
-        <v>131</v>
+        <v>68</v>
       </c>
       <c r="G207" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="H207" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="208" spans="1:8">
@@ -10636,10 +10599,10 @@
         <v>14</v>
       </c>
       <c r="C208" t="s">
-        <v>68</v>
+        <v>150</v>
       </c>
       <c r="D208" t="s">
-        <v>68</v>
+        <v>150</v>
       </c>
       <c r="G208" t="s">
         <v>139</v>
@@ -10656,16 +10619,19 @@
         <v>14</v>
       </c>
       <c r="C209" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D209" t="s">
-        <v>150</v>
+        <v>151</v>
+      </c>
+      <c r="E209" t="s">
+        <v>111</v>
       </c>
       <c r="G209" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="H209" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="210" spans="1:8">
@@ -10676,19 +10642,16 @@
         <v>14</v>
       </c>
       <c r="C210" t="s">
-        <v>151</v>
+        <v>167</v>
       </c>
       <c r="D210" t="s">
-        <v>151</v>
-      </c>
-      <c r="E210" t="s">
-        <v>111</v>
+        <v>167</v>
       </c>
       <c r="G210" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="H210" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="211" spans="1:8">
@@ -10699,16 +10662,19 @@
         <v>14</v>
       </c>
       <c r="C211" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="D211" t="s">
-        <v>167</v>
+        <v>168</v>
+      </c>
+      <c r="E211" t="s">
+        <v>155</v>
       </c>
       <c r="G211" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="H211" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="212" spans="1:8">
@@ -10719,13 +10685,13 @@
         <v>14</v>
       </c>
       <c r="C212" t="s">
-        <v>168</v>
+        <v>152</v>
       </c>
       <c r="D212" t="s">
-        <v>168</v>
+        <v>152</v>
       </c>
       <c r="E212" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="G212" t="s">
         <v>140</v>
@@ -10742,19 +10708,16 @@
         <v>14</v>
       </c>
       <c r="C213" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D213" t="s">
-        <v>152</v>
-      </c>
-      <c r="E213" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="G213" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="H213" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="214" spans="1:8">
@@ -10765,16 +10728,19 @@
         <v>14</v>
       </c>
       <c r="C214" t="s">
-        <v>153</v>
+        <v>69</v>
       </c>
       <c r="D214" t="s">
-        <v>153</v>
+        <v>69</v>
+      </c>
+      <c r="E214" t="s">
+        <v>117</v>
+      </c>
+      <c r="F214" t="s">
+        <v>117</v>
       </c>
       <c r="G214" t="s">
         <v>139</v>
-      </c>
-      <c r="H214" t="s">
-        <v>143</v>
       </c>
     </row>
     <row r="215" spans="1:8">
@@ -10785,16 +10751,16 @@
         <v>14</v>
       </c>
       <c r="C215" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D215" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E215" t="s">
-        <v>117</v>
+        <v>104</v>
       </c>
       <c r="F215" t="s">
-        <v>117</v>
+        <v>104</v>
       </c>
       <c r="G215" t="s">
         <v>139</v>
@@ -10808,19 +10774,16 @@
         <v>14</v>
       </c>
       <c r="C216" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D216" t="s">
-        <v>70</v>
-      </c>
-      <c r="E216" t="s">
-        <v>104</v>
-      </c>
-      <c r="F216" t="s">
-        <v>104</v>
+        <v>71</v>
       </c>
       <c r="G216" t="s">
         <v>139</v>
+      </c>
+      <c r="H216" t="s">
+        <v>143</v>
       </c>
     </row>
     <row r="217" spans="1:8">
@@ -10831,16 +10794,19 @@
         <v>14</v>
       </c>
       <c r="C217" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D217" t="s">
-        <v>71</v>
+        <v>72</v>
+      </c>
+      <c r="E217" t="s">
+        <v>106</v>
       </c>
       <c r="G217" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="H217" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="218" spans="1:8">
@@ -10851,19 +10817,19 @@
         <v>14</v>
       </c>
       <c r="C218" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D218" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E218" t="s">
-        <v>106</v>
+        <v>134</v>
+      </c>
+      <c r="F218" t="s">
+        <v>134</v>
       </c>
       <c r="G218" t="s">
-        <v>140</v>
-      </c>
-      <c r="H218" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
     </row>
     <row r="219" spans="1:8">
@@ -10874,16 +10840,16 @@
         <v>14</v>
       </c>
       <c r="C219" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D219" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E219" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F219" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="G219" t="s">
         <v>139</v>
@@ -10897,19 +10863,19 @@
         <v>14</v>
       </c>
       <c r="C220" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D220" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E220" t="s">
-        <v>135</v>
-      </c>
-      <c r="F220" t="s">
-        <v>135</v>
+        <v>109</v>
       </c>
       <c r="G220" t="s">
-        <v>139</v>
+        <v>140</v>
+      </c>
+      <c r="H220" t="s">
+        <v>142</v>
       </c>
     </row>
     <row r="221" spans="1:8">
@@ -10920,19 +10886,19 @@
         <v>14</v>
       </c>
       <c r="C221" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D221" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E221" t="s">
-        <v>109</v>
+        <v>105</v>
+      </c>
+      <c r="F221" t="s">
+        <v>105</v>
       </c>
       <c r="G221" t="s">
-        <v>140</v>
-      </c>
-      <c r="H221" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
     </row>
     <row r="222" spans="1:8">
@@ -10943,10 +10909,10 @@
         <v>14</v>
       </c>
       <c r="C222" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D222" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E222" t="s">
         <v>105</v>
@@ -10966,19 +10932,16 @@
         <v>14</v>
       </c>
       <c r="C223" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D223" t="s">
-        <v>77</v>
-      </c>
-      <c r="E223" t="s">
-        <v>105</v>
-      </c>
-      <c r="F223" t="s">
-        <v>105</v>
+        <v>78</v>
       </c>
       <c r="G223" t="s">
         <v>139</v>
+      </c>
+      <c r="H223" t="s">
+        <v>143</v>
       </c>
     </row>
     <row r="224" spans="1:8">
@@ -10989,16 +10952,19 @@
         <v>14</v>
       </c>
       <c r="C224" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D224" t="s">
-        <v>78</v>
+        <v>79</v>
+      </c>
+      <c r="E224" t="s">
+        <v>106</v>
       </c>
       <c r="G224" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="H224" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="225" spans="1:8">
@@ -11009,19 +10975,16 @@
         <v>14</v>
       </c>
       <c r="C225" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D225" t="s">
-        <v>79</v>
-      </c>
-      <c r="E225" t="s">
-        <v>106</v>
+        <v>80</v>
       </c>
       <c r="G225" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="H225" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="226" spans="1:8">
@@ -11032,16 +10995,19 @@
         <v>14</v>
       </c>
       <c r="C226" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D226" t="s">
-        <v>80</v>
+        <v>81</v>
+      </c>
+      <c r="E226" t="s">
+        <v>111</v>
       </c>
       <c r="G226" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="H226" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="227" spans="1:8">
@@ -11052,19 +11018,19 @@
         <v>14</v>
       </c>
       <c r="C227" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D227" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E227" t="s">
-        <v>111</v>
+        <v>112</v>
+      </c>
+      <c r="F227" t="s">
+        <v>112</v>
       </c>
       <c r="G227" t="s">
-        <v>140</v>
-      </c>
-      <c r="H227" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
     </row>
     <row r="228" spans="1:8">
@@ -11075,19 +11041,19 @@
         <v>14</v>
       </c>
       <c r="C228" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D228" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E228" t="s">
-        <v>112</v>
-      </c>
-      <c r="F228" t="s">
-        <v>112</v>
+        <v>155</v>
       </c>
       <c r="G228" t="s">
-        <v>139</v>
+        <v>140</v>
+      </c>
+      <c r="H228" t="s">
+        <v>142</v>
       </c>
     </row>
     <row r="229" spans="1:8">
@@ -11098,13 +11064,16 @@
         <v>14</v>
       </c>
       <c r="C229" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D229" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E229" t="s">
-        <v>155</v>
+        <v>116</v>
+      </c>
+      <c r="F229" t="s">
+        <v>131</v>
       </c>
       <c r="G229" t="s">
         <v>140</v>
@@ -11121,22 +11090,16 @@
         <v>14</v>
       </c>
       <c r="C230" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D230" t="s">
-        <v>84</v>
-      </c>
-      <c r="E230" t="s">
-        <v>116</v>
-      </c>
-      <c r="F230" t="s">
-        <v>131</v>
+        <v>85</v>
       </c>
       <c r="G230" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="H230" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="231" spans="1:8">
@@ -11147,16 +11110,19 @@
         <v>14</v>
       </c>
       <c r="C231" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D231" t="s">
-        <v>85</v>
+        <v>86</v>
+      </c>
+      <c r="E231" t="s">
+        <v>117</v>
       </c>
       <c r="G231" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="H231" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="232" spans="1:8">
@@ -11167,19 +11133,19 @@
         <v>14</v>
       </c>
       <c r="C232" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D232" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E232" t="s">
-        <v>117</v>
+        <v>104</v>
+      </c>
+      <c r="F232" t="s">
+        <v>104</v>
       </c>
       <c r="G232" t="s">
-        <v>140</v>
-      </c>
-      <c r="H232" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
     </row>
     <row r="233" spans="1:8">
@@ -11190,19 +11156,16 @@
         <v>14</v>
       </c>
       <c r="C233" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D233" t="s">
-        <v>87</v>
-      </c>
-      <c r="E233" t="s">
-        <v>104</v>
-      </c>
-      <c r="F233" t="s">
-        <v>104</v>
+        <v>88</v>
       </c>
       <c r="G233" t="s">
         <v>139</v>
+      </c>
+      <c r="H233" t="s">
+        <v>143</v>
       </c>
     </row>
     <row r="234" spans="1:8">
@@ -11213,16 +11176,19 @@
         <v>14</v>
       </c>
       <c r="C234" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D234" t="s">
-        <v>88</v>
+        <v>89</v>
+      </c>
+      <c r="E234" t="s">
+        <v>106</v>
       </c>
       <c r="G234" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="H234" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="235" spans="1:8">
@@ -11233,19 +11199,19 @@
         <v>14</v>
       </c>
       <c r="C235" t="s">
-        <v>89</v>
+        <v>100</v>
       </c>
       <c r="D235" t="s">
-        <v>89</v>
+        <v>100</v>
       </c>
       <c r="E235" t="s">
-        <v>106</v>
+        <v>182</v>
+      </c>
+      <c r="F235" t="s">
+        <v>137</v>
       </c>
       <c r="G235" t="s">
-        <v>140</v>
-      </c>
-      <c r="H235" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
     </row>
     <row r="236" spans="1:8">
@@ -11256,16 +11222,16 @@
         <v>14</v>
       </c>
       <c r="C236" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="D236" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="E236" t="s">
-        <v>182</v>
+        <v>136</v>
       </c>
       <c r="F236" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="G236" t="s">
         <v>139</v>
@@ -11279,19 +11245,19 @@
         <v>14</v>
       </c>
       <c r="C237" t="s">
-        <v>96</v>
+        <v>169</v>
       </c>
       <c r="D237" t="s">
-        <v>96</v>
+        <v>169</v>
       </c>
       <c r="E237" t="s">
-        <v>136</v>
-      </c>
-      <c r="F237" t="s">
-        <v>136</v>
+        <v>109</v>
       </c>
       <c r="G237" t="s">
-        <v>139</v>
+        <v>140</v>
+      </c>
+      <c r="H237" t="s">
+        <v>142</v>
       </c>
     </row>
     <row r="238" spans="1:8">
@@ -11302,19 +11268,19 @@
         <v>14</v>
       </c>
       <c r="C238" t="s">
-        <v>169</v>
+        <v>98</v>
       </c>
       <c r="D238" t="s">
-        <v>169</v>
+        <v>98</v>
       </c>
       <c r="E238" t="s">
-        <v>109</v>
+        <v>105</v>
+      </c>
+      <c r="F238" t="s">
+        <v>105</v>
       </c>
       <c r="G238" t="s">
-        <v>140</v>
-      </c>
-      <c r="H238" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
     </row>
     <row r="239" spans="1:8">
@@ -11325,10 +11291,10 @@
         <v>14</v>
       </c>
       <c r="C239" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D239" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E239" t="s">
         <v>105</v>
@@ -11348,19 +11314,16 @@
         <v>14</v>
       </c>
       <c r="C240" t="s">
-        <v>99</v>
+        <v>170</v>
       </c>
       <c r="D240" t="s">
-        <v>99</v>
-      </c>
-      <c r="E240" t="s">
-        <v>105</v>
-      </c>
-      <c r="F240" t="s">
-        <v>105</v>
+        <v>170</v>
       </c>
       <c r="G240" t="s">
         <v>139</v>
+      </c>
+      <c r="H240" t="s">
+        <v>143</v>
       </c>
     </row>
     <row r="241" spans="1:8">
@@ -11371,16 +11334,19 @@
         <v>14</v>
       </c>
       <c r="C241" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D241" t="s">
-        <v>170</v>
+        <v>171</v>
+      </c>
+      <c r="E241" t="s">
+        <v>106</v>
       </c>
       <c r="G241" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="H241" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="242" spans="1:8">
@@ -11391,19 +11357,16 @@
         <v>14</v>
       </c>
       <c r="C242" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="D242" t="s">
-        <v>171</v>
-      </c>
-      <c r="E242" t="s">
-        <v>106</v>
+        <v>172</v>
       </c>
       <c r="G242" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="H242" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="243" spans="1:8">
@@ -11414,16 +11377,19 @@
         <v>14</v>
       </c>
       <c r="C243" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D243" t="s">
-        <v>172</v>
+        <v>173</v>
+      </c>
+      <c r="E243" t="s">
+        <v>111</v>
       </c>
       <c r="G243" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="H243" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="244" spans="1:8">
@@ -11434,19 +11400,16 @@
         <v>14</v>
       </c>
       <c r="C244" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D244" t="s">
-        <v>173</v>
-      </c>
-      <c r="E244" t="s">
-        <v>111</v>
+        <v>174</v>
       </c>
       <c r="G244" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="H244" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="245" spans="1:8">
@@ -11457,16 +11420,19 @@
         <v>14</v>
       </c>
       <c r="C245" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="D245" t="s">
-        <v>174</v>
+        <v>175</v>
+      </c>
+      <c r="E245" t="s">
+        <v>155</v>
       </c>
       <c r="G245" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="H245" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="246" spans="1:8">
@@ -11477,13 +11443,13 @@
         <v>14</v>
       </c>
       <c r="C246" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="D246" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="E246" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="G246" t="s">
         <v>140</v>
@@ -11500,19 +11466,16 @@
         <v>14</v>
       </c>
       <c r="C247" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D247" t="s">
-        <v>176</v>
-      </c>
-      <c r="E247" t="s">
-        <v>158</v>
+        <v>177</v>
       </c>
       <c r="G247" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="H247" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="248" spans="1:8">
@@ -11523,16 +11486,19 @@
         <v>14</v>
       </c>
       <c r="C248" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D248" t="s">
-        <v>177</v>
+        <v>178</v>
+      </c>
+      <c r="E248" t="s">
+        <v>117</v>
       </c>
       <c r="G248" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="H248" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="249" spans="1:8">
@@ -11543,19 +11509,19 @@
         <v>14</v>
       </c>
       <c r="C249" t="s">
-        <v>178</v>
+        <v>97</v>
       </c>
       <c r="D249" t="s">
-        <v>178</v>
+        <v>97</v>
       </c>
       <c r="E249" t="s">
-        <v>117</v>
+        <v>104</v>
+      </c>
+      <c r="F249" t="s">
+        <v>104</v>
       </c>
       <c r="G249" t="s">
-        <v>140</v>
-      </c>
-      <c r="H249" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
     </row>
     <row r="250" spans="1:8">
@@ -11566,19 +11532,16 @@
         <v>14</v>
       </c>
       <c r="C250" t="s">
-        <v>97</v>
+        <v>179</v>
       </c>
       <c r="D250" t="s">
-        <v>97</v>
-      </c>
-      <c r="E250" t="s">
-        <v>104</v>
-      </c>
-      <c r="F250" t="s">
-        <v>104</v>
+        <v>179</v>
       </c>
       <c r="G250" t="s">
         <v>139</v>
+      </c>
+      <c r="H250" t="s">
+        <v>143</v>
       </c>
     </row>
     <row r="251" spans="1:8">
@@ -11589,16 +11552,19 @@
         <v>14</v>
       </c>
       <c r="C251" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="D251" t="s">
-        <v>179</v>
+        <v>180</v>
+      </c>
+      <c r="E251" t="s">
+        <v>106</v>
       </c>
       <c r="G251" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="H251" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="252" spans="1:8">
@@ -11609,13 +11575,13 @@
         <v>14</v>
       </c>
       <c r="C252" t="s">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="D252" t="s">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="E252" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="G252" t="s">
         <v>140</v>
@@ -11632,13 +11598,13 @@
         <v>14</v>
       </c>
       <c r="C253" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D253" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E253" t="s">
-        <v>102</v>
+        <v>183</v>
       </c>
       <c r="G253" t="s">
         <v>140</v>
@@ -11655,19 +11621,16 @@
         <v>14</v>
       </c>
       <c r="C254" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D254" t="s">
-        <v>91</v>
-      </c>
-      <c r="E254" t="s">
-        <v>183</v>
+        <v>92</v>
       </c>
       <c r="G254" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="H254" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="255" spans="1:8">
@@ -11678,16 +11641,19 @@
         <v>14</v>
       </c>
       <c r="C255" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D255" t="s">
-        <v>92</v>
+        <v>93</v>
+      </c>
+      <c r="E255" t="s">
+        <v>106</v>
       </c>
       <c r="G255" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="H255" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="256" spans="1:8">
@@ -11698,13 +11664,13 @@
         <v>14</v>
       </c>
       <c r="C256" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D256" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E256" t="s">
-        <v>106</v>
+        <v>184</v>
       </c>
       <c r="G256" t="s">
         <v>140</v>
@@ -11713,7 +11679,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="257" spans="1:8">
+    <row r="257" spans="1:7">
       <c r="A257">
         <v>3</v>
       </c>
@@ -11721,22 +11687,16 @@
         <v>14</v>
       </c>
       <c r="C257" t="s">
-        <v>94</v>
-      </c>
-      <c r="D257" t="s">
-        <v>94</v>
-      </c>
-      <c r="E257" t="s">
-        <v>184</v>
+        <v>95</v>
+      </c>
+      <c r="F257" t="s">
+        <v>121</v>
       </c>
       <c r="G257" t="s">
-        <v>140</v>
-      </c>
-      <c r="H257" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="258" spans="1:8">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="258" spans="1:7">
       <c r="A258">
         <v>3</v>
       </c>
@@ -11744,46 +11704,12 @@
         <v>14</v>
       </c>
       <c r="C258" t="s">
-        <v>44</v>
+        <v>101</v>
       </c>
       <c r="F258" t="s">
-        <v>130</v>
+        <v>138</v>
       </c>
       <c r="G258" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="259" spans="1:8">
-      <c r="A259">
-        <v>3</v>
-      </c>
-      <c r="B259" t="s">
-        <v>14</v>
-      </c>
-      <c r="C259" t="s">
-        <v>95</v>
-      </c>
-      <c r="F259" t="s">
-        <v>121</v>
-      </c>
-      <c r="G259" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="260" spans="1:8">
-      <c r="A260">
-        <v>3</v>
-      </c>
-      <c r="B260" t="s">
-        <v>14</v>
-      </c>
-      <c r="C260" t="s">
-        <v>101</v>
-      </c>
-      <c r="F260" t="s">
-        <v>138</v>
-      </c>
-      <c r="G260" t="s">
         <v>141</v>
       </c>
     </row>
